--- a/UCLStats25-26.xlsx
+++ b/UCLStats25-26.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johntran/VSCode/VSCode for ACM/mpacmphase2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE72912B-4ED0-1249-8599-8AAD8B8DA42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8ACBB9-78F2-5243-B847-7C3EBD1F266C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17100" xr2:uid="{802A0F31-8C0E-1546-A7F6-97F3B02C124B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -134,12 +134,6 @@
     <t>GamesPlayed</t>
   </si>
   <si>
-    <t>RedCards</t>
-  </si>
-  <si>
-    <t>YellowCards</t>
-  </si>
-  <si>
     <t>Goals</t>
   </si>
   <si>
@@ -155,9 +149,6 @@
     <t>Passes</t>
   </si>
   <si>
-    <t>Fouls</t>
-  </si>
-  <si>
     <t>SucessfulTackles</t>
   </si>
   <si>
@@ -168,6 +159,15 @@
   </si>
   <si>
     <t>AccuratePasses</t>
+  </si>
+  <si>
+    <t>GoalsConceded</t>
+  </si>
+  <si>
+    <t>FoulsCommitted</t>
+  </si>
+  <si>
+    <t>Tackles</t>
   </si>
 </sst>
 </file>
@@ -552,12 +552,12 @@
     <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -574,40 +574,40 @@
         <v>31</v>
       </c>
       <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>38</v>
-      </c>
-      <c r="J1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
       </c>
       <c r="O1" t="s">
         <v>41</v>
       </c>
       <c r="P1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -623,8 +623,11 @@
       <c r="D2">
         <v>7</v>
       </c>
+      <c r="N2">
+        <v>16</v>
+      </c>
       <c r="O2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -643,6 +646,15 @@
       <c r="D3">
         <v>4</v>
       </c>
+      <c r="N3">
+        <v>10</v>
+      </c>
+      <c r="O3">
+        <v>6</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -657,12 +669,6 @@
       <c r="D4">
         <v>8</v>
       </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -677,12 +683,6 @@
       <c r="D5">
         <v>9</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -697,12 +697,6 @@
       <c r="D6">
         <v>8</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -717,12 +711,6 @@
       <c r="D7">
         <v>7</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -737,9 +725,6 @@
       <c r="D8">
         <v>2</v>
       </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -754,9 +739,6 @@
       <c r="D9">
         <v>10</v>
       </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -771,12 +753,6 @@
       <c r="D10">
         <v>4</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -791,12 +767,6 @@
       <c r="D11">
         <v>9</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -808,6 +778,9 @@
       <c r="C12" t="s">
         <v>27</v>
       </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -819,6 +792,18 @@
       <c r="C13" t="s">
         <v>27</v>
       </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -830,6 +815,9 @@
       <c r="C14" t="s">
         <v>27</v>
       </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -841,6 +829,9 @@
       <c r="C15" t="s">
         <v>27</v>
       </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -852,8 +843,11 @@
       <c r="C16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -863,8 +857,11 @@
       <c r="C17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -874,8 +871,11 @@
       <c r="C18" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -885,8 +885,11 @@
       <c r="C19" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -896,8 +899,11 @@
       <c r="C20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -907,8 +913,11 @@
       <c r="C21" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -918,8 +927,11 @@
       <c r="C22" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -929,8 +941,11 @@
       <c r="C23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -939,6 +954,9 @@
       </c>
       <c r="C24" t="s">
         <v>5</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/UCLStats25-26.xlsx
+++ b/UCLStats25-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johntran/VSCode/VSCode for ACM/mpacmphase2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8ACBB9-78F2-5243-B847-7C3EBD1F266C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF233119-F28C-5D4D-9C12-7EF27B50F4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17100" xr2:uid="{802A0F31-8C0E-1546-A7F6-97F3B02C124B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="60">
   <si>
     <t>Player</t>
   </si>
@@ -168,6 +168,54 @@
   </si>
   <si>
     <t>Tackles</t>
+  </si>
+  <si>
+    <t>Thibaut Courtois</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Gianluigi Donnarumma</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Jonathan Tah</t>
+  </si>
+  <si>
+    <t>FC Bayern</t>
+  </si>
+  <si>
+    <t>Marc Cucurella</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Vitinha</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Zubimendi </t>
+  </si>
+  <si>
+    <t>Victor Osimhen</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Julián Alvarez</t>
+  </si>
+  <si>
+    <t>Atlético Madrid</t>
   </si>
 </sst>
 </file>
@@ -539,11 +587,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A256F4E6-B428-C94B-9C3F-FFCDE50E4C61}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" customWidth="1"/>
@@ -669,6 +717,15 @@
       <c r="D4">
         <v>8</v>
       </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>8</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -683,6 +740,15 @@
       <c r="D5">
         <v>9</v>
       </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>14</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -697,6 +763,15 @@
       <c r="D6">
         <v>8</v>
       </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -711,6 +786,15 @@
       <c r="D7">
         <v>7</v>
       </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -725,6 +809,15 @@
       <c r="D8">
         <v>2</v>
       </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -739,6 +832,15 @@
       <c r="D9">
         <v>10</v>
       </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -753,6 +855,15 @@
       <c r="D10">
         <v>4</v>
       </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -767,6 +878,15 @@
       <c r="D11">
         <v>9</v>
       </c>
+      <c r="K11">
+        <v>12</v>
+      </c>
+      <c r="L11">
+        <v>17</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -781,6 +901,15 @@
       <c r="D12">
         <v>7</v>
       </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>454</v>
+      </c>
+      <c r="J12">
+        <v>409</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -818,6 +947,15 @@
       <c r="D14">
         <v>7</v>
       </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>407</v>
+      </c>
+      <c r="J14">
+        <v>383</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -832,6 +970,15 @@
       <c r="D15">
         <v>8</v>
       </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>156</v>
+      </c>
+      <c r="J15">
+        <v>136</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -846,8 +993,17 @@
       <c r="D16">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16">
+        <v>285</v>
+      </c>
+      <c r="J16">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -860,8 +1016,17 @@
       <c r="D17">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>129</v>
+      </c>
+      <c r="J17">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -874,8 +1039,17 @@
       <c r="D18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>162</v>
+      </c>
+      <c r="J18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -888,8 +1062,17 @@
       <c r="D19">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>23</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -902,8 +1085,17 @@
       <c r="D20">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>28</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -916,8 +1108,17 @@
       <c r="D21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -930,8 +1131,17 @@
       <c r="D22">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -944,8 +1154,17 @@
       <c r="D23">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23">
+        <v>23</v>
+      </c>
+      <c r="G23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -957,6 +1176,199 @@
       </c>
       <c r="D24">
         <v>4</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25">
+        <v>11</v>
+      </c>
+      <c r="N25">
+        <v>56</v>
+      </c>
+      <c r="O25">
+        <v>11</v>
+      </c>
+      <c r="P25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26">
+        <v>9</v>
+      </c>
+      <c r="N26">
+        <v>23</v>
+      </c>
+      <c r="O26">
+        <v>12</v>
+      </c>
+      <c r="P26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="K27">
+        <v>19</v>
+      </c>
+      <c r="L27">
+        <v>14</v>
+      </c>
+      <c r="M27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>9</v>
+      </c>
+      <c r="K28">
+        <v>14</v>
+      </c>
+      <c r="L28">
+        <v>24</v>
+      </c>
+      <c r="M28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29">
+        <v>12</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1189</v>
+      </c>
+      <c r="J29">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>387</v>
+      </c>
+      <c r="J30">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
+      </c>
+      <c r="F31">
+        <v>25</v>
+      </c>
+      <c r="G31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32">
+        <v>11</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>38</v>
+      </c>
+      <c r="G32">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
